--- a/artfynd/A 3947-2021 artfynd.xlsx
+++ b/artfynd/A 3947-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129943209</v>
       </c>
       <c r="B2" t="n">
-        <v>102061</v>
+        <v>102065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3947-2021 artfynd.xlsx
+++ b/artfynd/A 3947-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129943209</v>
       </c>
       <c r="B2" t="n">
-        <v>102065</v>
+        <v>102068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3947-2021 artfynd.xlsx
+++ b/artfynd/A 3947-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129943209</v>
       </c>
       <c r="B2" t="n">
-        <v>102068</v>
+        <v>102069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3947-2021 artfynd.xlsx
+++ b/artfynd/A 3947-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129943209</v>
       </c>
       <c r="B2" t="n">
-        <v>102069</v>
+        <v>102086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3947-2021 artfynd.xlsx
+++ b/artfynd/A 3947-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129943209</v>
       </c>
       <c r="B2" t="n">
-        <v>102102</v>
+        <v>102104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3947-2021 artfynd.xlsx
+++ b/artfynd/A 3947-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129943209</v>
       </c>
       <c r="B2" t="n">
-        <v>102104</v>
+        <v>102191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
